--- a/Vulnerability Test Results/E2E_Functional_Test_Report_Latest.xlsx
+++ b/Vulnerability Test Results/E2E_Functional_Test_Report_Latest.xlsx
@@ -32,7 +32,7 @@
     <t>Test Execution Date</t>
   </si>
   <si>
-    <t>01/07/2026</t>
+    <t>7/20/2026</t>
   </si>
   <si>
     <t>Automation Tool</t>

--- a/Vulnerability Test Results/E2E_Functional_Test_Report_Latest.xlsx
+++ b/Vulnerability Test Results/E2E_Functional_Test_Report_Latest.xlsx
@@ -32,7 +32,7 @@
     <t>Test Execution Date</t>
   </si>
   <si>
-    <t>7/20/2026</t>
+    <t>8/31/2026</t>
   </si>
   <si>
     <t>Automation Tool</t>
